--- a/data/fmsForecastOutput/File1/RPT_RPT8255149037738UH_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT8255149037738UH_fmsForecastOutput.xlsx
@@ -1875,22 +1875,22 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>168.8311543927491</v>
+        <v>168.8311543927489</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>171.6192926502704</v>
+        <v>171.6192926502703</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>186.1133617763841</v>
+        <v>186.113361776384</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>186.8670719411977</v>
+        <v>186.8670719411976</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>199.3871886405418</v>
+        <v>199.3871886405417</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>153.2773507664425</v>
+        <v>153.2773507664423</v>
       </c>
       <c r="I8" s="149" t="n">
         <v>123.7135916151328</v>
@@ -1899,25 +1899,25 @@
         <v>108.6520621690502</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>100.0144596206879</v>
+        <v>100.0144596206878</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>98.3707292968612</v>
+        <v>98.37072929686116</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>25738.41694166523</v>
+        <v>25738.41694166521</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>23878.37006924578</v>
+        <v>23878.37006924577</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>25281.1803768556</v>
+        <v>25281.18037685559</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>24403.3529981302</v>
+        <v>24403.35299813019</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>24657.8453057521</v>
+        <v>24657.84530575209</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,22 +1925,22 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>181.1736063235402</v>
+        <v>181.1736063235401</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>184.1655722605182</v>
+        <v>184.1655722605181</v>
       </c>
       <c r="V8" s="149" t="n">
         <v>199.7192346359587</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>200.5280450073215</v>
+        <v>200.5280450073214</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>213.9634485746927</v>
+        <v>213.9634485746926</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>163.3823689554769</v>
+        <v>163.3823689554768</v>
       </c>
       <c r="Z8" s="149" t="n">
         <v>130.1027599816049</v>
@@ -1949,25 +1949,25 @@
         <v>113.1522444761571</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>103.7991497142621</v>
+        <v>103.799149714262</v>
       </c>
       <c r="AC8" s="150" t="n">
         <v>101.7920111315501</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>25738.41694166523</v>
+        <v>25738.41694166521</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>23878.37006924578</v>
+        <v>23878.37006924577</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>25281.1803768556</v>
+        <v>25281.18037685559</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>24403.3529981302</v>
+        <v>24403.35299813019</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>24657.8453057521</v>
+        <v>24657.84530575209</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
         <v>295.4733399463256</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>325.496709462285</v>
+        <v>325.4967094622849</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>348.9888334192068</v>
+        <v>348.9888334192067</v>
       </c>
       <c r="H9" s="155" t="n">
         <v>201.8376410651477</v>
@@ -2046,10 +2046,10 @@
         <v>162.7879524735079</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>175.1737350997654</v>
+        <v>175.1737350997653</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>184.9182253190965</v>
+        <v>184.9182253190964</v>
       </c>
       <c r="M9" s="158" t="n">
         <v>21920.16704500929</v>
@@ -2064,7 +2064,7 @@
         <v>27944.82763295536</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>31006.08140484352</v>
+        <v>31006.08140484351</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2081,10 +2081,10 @@
         <v>297.601781808558</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>327.8414246320673</v>
+        <v>327.8414246320672</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>351.502774076716</v>
+        <v>351.5027740767158</v>
       </c>
       <c r="Y9" s="155" t="n">
         <v>202.9296303802722</v>
@@ -2096,10 +2096,10 @@
         <v>163.4319246736625</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>175.8505851577324</v>
+        <v>175.8505851577323</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>185.6216589052937</v>
+        <v>185.6216589052936</v>
       </c>
       <c r="AD9" s="158" t="n">
         <v>21920.16704500929</v>
@@ -2114,7 +2114,7 @@
         <v>27944.82763295536</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>31006.08140484352</v>
+        <v>31006.08140484351</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>203.5272933931917</v>
+        <v>203.5272933931916</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>205.4251686871783</v>
@@ -2179,7 +2179,7 @@
         <v>227.4317781554929</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>241.8545153418868</v>
+        <v>241.8545153418867</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>261.9310829378509</v>
@@ -2188,7 +2188,7 @@
         <v>172.3491162682639</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>139.6995694680196</v>
+        <v>139.6995694680195</v>
       </c>
       <c r="J10" s="162" t="n">
         <v>129.8478867266897</v>
@@ -2200,19 +2200,19 @@
         <v>133.0600198382123</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>47658.58398667451</v>
+        <v>47658.58398667449</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>45004.6094059863</v>
+        <v>45004.60940598629</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>49654.09622186436</v>
+        <v>49654.09622186435</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>52348.18063108556</v>
+        <v>52348.18063108554</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>55663.92671059562</v>
+        <v>55663.9267105956</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,22 +2220,22 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>213.5308143211516</v>
+        <v>213.5308143211515</v>
       </c>
       <c r="U10" s="162" t="n">
         <v>215.3022297036462</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>238.1704445553959</v>
+        <v>238.1704445553958</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>252.97003181205</v>
+        <v>252.9700318120499</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>273.5955661477936</v>
+        <v>273.5955661477935</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>179.4689193169638</v>
+        <v>179.4689193169637</v>
       </c>
       <c r="Z10" s="162" t="n">
         <v>144.1982014686534</v>
@@ -2247,22 +2247,22 @@
         <v>132.8586804826105</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>136.0056203622418</v>
+        <v>136.0056203622417</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>47658.58398667451</v>
+        <v>47658.58398667449</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>45004.6094059863</v>
+        <v>45004.60940598629</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>49654.09622186436</v>
+        <v>49654.09622186435</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>52348.18063108556</v>
+        <v>52348.18063108554</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>55663.92671059562</v>
+        <v>55663.9267105956</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>566.6054680354947</v>
+        <v>566.6054680354948</v>
       </c>
       <c r="D11" s="156" t="n">
         <v>612.6808519631295</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>723.0747664052132</v>
+        <v>723.0747664052133</v>
       </c>
       <c r="F11" s="156" t="n">
         <v>904.7079682969697</v>
@@ -2339,7 +2339,7 @@
         <v>451.8271444481675</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>471.6648997117882</v>
+        <v>471.6648997117883</v>
       </c>
       <c r="K11" s="156" t="n">
         <v>532.499701039077</v>
@@ -2368,13 +2368,13 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>703.8005813633506</v>
+        <v>703.8005813633507</v>
       </c>
       <c r="U11" s="156" t="n">
         <v>761.03243637393</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>898.1566004464997</v>
+        <v>898.1566004465</v>
       </c>
       <c r="W11" s="156" t="n">
         <v>1123.769589197778</v>
@@ -2383,13 +2383,13 @@
         <v>1230.811698764978</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>556.0812988437804</v>
+        <v>556.0812988437806</v>
       </c>
       <c r="Z11" s="156" t="n">
         <v>527.6852489088582</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>540.3775448966164</v>
+        <v>540.3775448966165</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>601.5151907494834</v>
@@ -2464,19 +2464,19 @@
         <v>292.9334129257201</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>313.8053478557997</v>
+        <v>313.8053478557995</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>362.9989687572868</v>
+        <v>362.9989687572867</v>
       </c>
       <c r="F12" s="162" t="n">
         <v>421.8103659669924</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>469.6809338134884</v>
+        <v>469.6809338134883</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>246.3659891868345</v>
+        <v>246.3659891868344</v>
       </c>
       <c r="I12" s="162" t="n">
         <v>217.9181417806051</v>
@@ -2488,16 +2488,16 @@
         <v>231.8352693063713</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>244.719548052216</v>
+        <v>244.7195480522159</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>91003.28694314421</v>
+        <v>91003.28694314418</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>93678.62704280759</v>
+        <v>93678.62704280758</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>109089.8541592967</v>
+        <v>109089.8541592966</v>
       </c>
       <c r="P12" s="165" t="n">
         <v>125321.9415528883</v>
@@ -2511,19 +2511,19 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>319.5568689679961</v>
+        <v>319.556868967996</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>343.1604862544158</v>
+        <v>343.1604862544157</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>397.1863209141925</v>
+        <v>397.1863209141924</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>460.9612145023847</v>
+        <v>460.9612145023846</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>513.8962342949286</v>
+        <v>513.8962342949285</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>264.929422797844</v>
@@ -2538,16 +2538,16 @@
         <v>243.1874751052183</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>256.205066129225</v>
+        <v>256.2050661292249</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>91003.28694314421</v>
+        <v>91003.28694314418</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>93678.62704280759</v>
+        <v>93678.62704280758</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>109089.8541592967</v>
+        <v>109089.8541592966</v>
       </c>
       <c r="AG12" s="165" t="n">
         <v>125321.9415528883</v>
@@ -2603,46 +2603,46 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>245.5649990194621</v>
+        <v>245.564999019462</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>362.5762081422322</v>
+        <v>362.576208142232</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>392.6941139741028</v>
+        <v>392.6941139741025</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>417.8253527933692</v>
+        <v>417.825352793369</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>447.7903039096206</v>
+        <v>447.7903039096204</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>245.5649990194621</v>
+        <v>245.564999019462</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>362.5762081422322</v>
+        <v>362.576208142232</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>392.6941139741028</v>
+        <v>392.6941139741025</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>417.8253527933692</v>
+        <v>417.825352793369</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>447.7903039096206</v>
+        <v>447.7903039096204</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>736.4368637819756</v>
+        <v>736.4368637819754</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>805.1896113223746</v>
+        <v>805.1896113223743</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>898.5758174492481</v>
+        <v>898.5758174492476</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>975.4712887117287</v>
+        <v>975.4712887117282</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>1066.629990298585</v>
@@ -2653,46 +2653,46 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>40.92749983657703</v>
+        <v>40.92749983657701</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>60.42936802370537</v>
+        <v>60.42936802370534</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>65.4490189956838</v>
+        <v>65.44901899568376</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>69.63755879889489</v>
+        <v>69.63755879889484</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>74.63171731827011</v>
+        <v>74.63171731827008</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>40.92749983657703</v>
+        <v>40.92749983657701</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>60.42936802370537</v>
+        <v>60.42936802370534</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>65.4490189956838</v>
+        <v>65.44901899568376</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>69.63755879889489</v>
+        <v>69.63755879889484</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>74.63171731827011</v>
+        <v>74.63171731827008</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>736.4368637819756</v>
+        <v>736.4368637819754</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>805.1896113223746</v>
+        <v>805.1896113223743</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>898.5758174492481</v>
+        <v>898.5758174492476</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>975.4712887117287</v>
+        <v>975.4712887117282</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>1066.629990298585</v>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>292.480518044717</v>
+        <v>292.4805180447171</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>314.1654786926691</v>
+        <v>314.165478692669</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>363.2233634397903</v>
+        <v>363.2233634397902</v>
       </c>
       <c r="F14" s="168" t="n">
         <v>421.7792960375185</v>
@@ -2761,7 +2761,7 @@
         <v>469.5068928948636</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>246.3595384668183</v>
+        <v>246.3595384668182</v>
       </c>
       <c r="I14" s="168" t="n">
         <v>218.6616000720948</v>
@@ -2776,7 +2776,7 @@
         <v>245.5639771297504</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>91739.72380692619</v>
+        <v>91739.72380692618</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>94483.81665412996</v>
@@ -2796,13 +2796,13 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>302.9980412125122</v>
+        <v>302.9980412125121</v>
       </c>
       <c r="U14" s="168" t="n">
         <v>330.0026720504127</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>381.3930646596941</v>
+        <v>381.393064659694</v>
       </c>
       <c r="W14" s="168" t="n">
         <v>441.7866635409871</v>
@@ -2811,13 +2811,13 @@
         <v>491.9408329024823</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>253.7795172218293</v>
+        <v>253.7795172218292</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>226.217766820759</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>221.6271521352697</v>
+        <v>221.6271521352696</v>
       </c>
       <c r="AB14" s="168" t="n">
         <v>238.5948398619033</v>
@@ -2826,7 +2826,7 @@
         <v>251.5641550335367</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>91739.72380692619</v>
+        <v>91739.72380692618</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>94483.81665412996</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="C22" s="79" t="n">
-        <v>76.49891397404303</v>
+        <v>76.49891397404302</v>
       </c>
       <c r="D22" s="80" t="n">
         <v>79.4443264888429</v>
       </c>
       <c r="E22" s="80" t="n">
-        <v>82.19863380507508</v>
+        <v>82.19863380507506</v>
       </c>
       <c r="F22" s="80" t="n">
         <v>80.66001790519121</v>
@@ -3616,13 +3616,13 @@
         </is>
       </c>
       <c r="T22" s="79" t="n">
-        <v>61.58662567812256</v>
+        <v>61.58662567812254</v>
       </c>
       <c r="U22" s="80" t="n">
         <v>63.95787526315834</v>
       </c>
       <c r="V22" s="80" t="n">
-        <v>66.17527267281126</v>
+        <v>66.17527267281125</v>
       </c>
       <c r="W22" s="80" t="n">
         <v>64.93658631027404</v>
@@ -3646,7 +3646,7 @@
         <v>67.40054441000001</v>
       </c>
       <c r="AD22" s="79" t="n">
-        <v>77.94670140246257</v>
+        <v>77.94670140246254</v>
       </c>
       <c r="AE22" s="80" t="n">
         <v>92.24062589861833</v>
@@ -3706,7 +3706,7 @@
         <v>310.6620239536148</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>298.5246353604367</v>
+        <v>298.5246353604368</v>
       </c>
       <c r="E23" s="86" t="n">
         <v>300.5238679678944</v>
@@ -3739,13 +3739,13 @@
         <v>429.8798910332167</v>
       </c>
       <c r="O23" s="86" t="n">
-        <v>508.4147154571744</v>
+        <v>508.4147154571743</v>
       </c>
       <c r="P23" s="86" t="n">
         <v>540.5646083438444</v>
       </c>
       <c r="Q23" s="87" t="n">
-        <v>570.444791155865</v>
+        <v>570.4447911558651</v>
       </c>
       <c r="S23" s="42" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>313.660972772553</v>
       </c>
       <c r="D25" s="92" t="n">
-        <v>300.7453812153509</v>
+        <v>300.745381215351</v>
       </c>
       <c r="E25" s="92" t="n">
         <v>302.8121014439594</v>
@@ -3984,7 +3984,7 @@
         <v>542.899247164084</v>
       </c>
       <c r="Q25" s="93" t="n">
-        <v>572.8267766097391</v>
+        <v>572.8267766097392</v>
       </c>
       <c r="S25" s="51" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>417.6675332888115</v>
       </c>
       <c r="AF25" s="92" t="n">
-        <v>496.2768727435288</v>
+        <v>496.2768727435289</v>
       </c>
       <c r="AG25" s="92" t="n">
         <v>529.3384086374205</v>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>171.8792907918565</v>
+        <v>171.8792907918564</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>179.2220110803922</v>
+        <v>179.2220110803921</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>195.907882372609</v>
+        <v>195.9078823726088</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>199.3146296083649</v>
+        <v>199.3146296083648</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>213.1926627868785</v>
+        <v>213.1926627868784</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>156.0446733835886</v>
+        <v>156.0446733835885</v>
       </c>
       <c r="I35" s="149" t="n">
         <v>129.1940920210261</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>114.3700549589269</v>
+        <v>114.3700549589268</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>106.6766058230473</v>
+        <v>106.6766058230472</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>105.1818718247416</v>
+        <v>105.1818718247415</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>26203.10727572991</v>
+        <v>26203.10727572989</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>24936.17960454477</v>
+        <v>24936.17960454476</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>26611.64391549987</v>
+        <v>26611.64391549986</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>26028.90500448929</v>
+        <v>26028.90500448928</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>26365.14279158321</v>
+        <v>26365.1427915832</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,22 +4458,22 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>184.4445776438433</v>
+        <v>184.4445776438432</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>192.3240896905617</v>
+        <v>192.3240896905616</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>210.2297865836179</v>
+        <v>210.2297865836178</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>213.8855850928127</v>
+        <v>213.8855850928126</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>228.7781760288434</v>
+        <v>228.7781760288433</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>166.3321310866241</v>
+        <v>166.3321310866239</v>
       </c>
       <c r="Z35" s="149" t="n">
         <v>135.8662999417511</v>
@@ -4488,19 +4488,19 @@
         <v>108.840041587076</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>26203.10727572991</v>
+        <v>26203.10727572989</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>24936.17960454477</v>
+        <v>24936.17960454476</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>26611.64391549987</v>
+        <v>26611.64391549986</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>26028.90500448929</v>
+        <v>26028.90500448928</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>26365.14279158321</v>
+        <v>26365.1427915832</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4519,10 +4519,10 @@
         <v>310.485521541103</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>346.3989019796252</v>
+        <v>346.3989019796251</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>372.3484651943248</v>
+        <v>372.3484651943247</v>
       </c>
       <c r="H36" s="155" t="n">
         <v>204.9039204600244</v>
@@ -4537,7 +4537,7 @@
         <v>186.4227432420769</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>197.2957607538008</v>
+        <v>197.2957607538007</v>
       </c>
       <c r="M36" s="158" t="n">
         <v>22253.17409061121</v>
@@ -4549,10 +4549,10 @@
         <v>25611.23615751466</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>29739.34091087101</v>
+        <v>29739.340910871</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>33081.47916846324</v>
+        <v>33081.47916846322</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>348.8941860690076</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>375.0306769322824</v>
+        <v>375.0306769322822</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>206.0124990709745</v>
@@ -4587,7 +4587,7 @@
         <v>187.1430581026232</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>198.0462787965145</v>
+        <v>198.0462787965144</v>
       </c>
       <c r="AD36" s="158" t="n">
         <v>22253.17409061121</v>
@@ -4599,10 +4599,10 @@
         <v>25611.23615751466</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>29739.34091087101</v>
+        <v>29739.340910871</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>33081.47916846324</v>
+        <v>33081.47916846322</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,19 +4612,19 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>206.9338819875104</v>
+        <v>206.9338819875103</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>214.5051045459706</v>
+        <v>214.5051045459705</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>239.1976368341762</v>
+        <v>239.1976368341761</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>257.6556037807597</v>
+        <v>257.6556037807596</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>279.730859591479</v>
+        <v>279.7308595914789</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>175.2338523836611</v>
@@ -4636,25 +4636,25 @@
         <v>136.5653819568742</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>138.2028388185149</v>
+        <v>138.2028388185148</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>142.1022404409862</v>
+        <v>142.1022404409861</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>48456.28136634112</v>
+        <v>48456.28136634111</v>
       </c>
       <c r="N37" s="165" t="n">
         <v>46993.84455846476</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>52222.88007301453</v>
+        <v>52222.88007301452</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>55768.2459153603</v>
+        <v>55768.24591536028</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>59446.62196004645</v>
+        <v>59446.62196004642</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>217.1048393301549</v>
+        <v>217.1048393301548</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>224.8187385543267</v>
+        <v>224.8187385543266</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>250.4918528247455</v>
+        <v>250.4918528247454</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>269.4973306280189</v>
+        <v>269.4973306280188</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>292.1880138872211</v>
+        <v>292.188013887221</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>182.4728249032223</v>
+        <v>182.4728249032222</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>150.5718626351797</v>
+        <v>150.5718626351796</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>140.1737677970666</v>
+        <v>140.1737677970665</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>141.5387407130763</v>
+        <v>141.5387407130762</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>145.24801205907</v>
+        <v>145.2480120590699</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>48456.28136634112</v>
+        <v>48456.28136634111</v>
       </c>
       <c r="AE37" s="165" t="n">
         <v>46993.84455846476</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>52222.88007301453</v>
+        <v>52222.88007301452</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>55768.2459153603</v>
+        <v>55768.24591536028</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>59446.62196004645</v>
+        <v>59446.62196004642</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,13 +4714,13 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>579.1549261281195</v>
+        <v>579.1549261281197</v>
       </c>
       <c r="D38" s="156" t="n">
         <v>640.6766384545072</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>760.6964866649363</v>
+        <v>760.6964866649364</v>
       </c>
       <c r="F38" s="156" t="n">
         <v>963.0963467162363</v>
@@ -4735,7 +4735,7 @@
         <v>472.4728953745258</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>496.2057158731739</v>
+        <v>496.205715873174</v>
       </c>
       <c r="K38" s="156" t="n">
         <v>566.8663642518962</v>
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>719.3887046689855</v>
+        <v>719.3887046689856</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>795.8069874856066</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>944.8878624699431</v>
+        <v>944.8878624699433</v>
       </c>
       <c r="W38" s="156" t="n">
         <v>1196.295847757939</v>
@@ -4779,13 +4779,13 @@
         <v>1311.676417067982</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>568.3976624329423</v>
+        <v>568.3976624329425</v>
       </c>
       <c r="Z38" s="156" t="n">
         <v>551.7972535777928</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>568.4934933064985</v>
+        <v>568.4934933064986</v>
       </c>
       <c r="AB38" s="156" t="n">
         <v>640.3360012354696</v>
@@ -4819,43 +4819,43 @@
         <v>298.5913857681865</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>327.9192301145427</v>
+        <v>327.9192301145426</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>381.8368663797842</v>
+        <v>381.8368663797841</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>449.1733342755009</v>
+        <v>449.1733342755008</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>500.9615586689945</v>
+        <v>500.9615586689944</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>251.1245179671615</v>
+        <v>251.1245179671614</v>
       </c>
       <c r="I39" s="162" t="n">
         <v>227.7193482168602</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>225.7037188902112</v>
+        <v>225.7037188902111</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>246.8744946044077</v>
+        <v>246.8744946044076</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>261.0178046479802</v>
+        <v>261.0178046479801</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>92761.00423785939</v>
+        <v>92761.00423785936</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>97891.96859761899</v>
+        <v>97891.96859761898</v>
       </c>
       <c r="O39" s="165" t="n">
         <v>114751.0920171928</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>133451.6144859162</v>
+        <v>133451.6144859161</v>
       </c>
       <c r="Q39" s="166" t="n">
         <v>148896.2470603794</v>
@@ -4866,46 +4866,46 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>325.7290705894716</v>
+        <v>325.7290705894715</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>358.5946613949664</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>417.7983774058482</v>
+        <v>417.7983774058481</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>490.8639104092637</v>
+        <v>490.8639104092636</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>548.1215863634466</v>
+        <v>548.1215863634465</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>270.0465020152312</v>
+        <v>270.0465020152311</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>242.1012717350669</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>237.8027006719695</v>
+        <v>237.8027006719694</v>
       </c>
       <c r="AB39" s="162" t="n">
         <v>258.9631214885767</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>273.2682551639558</v>
+        <v>273.2682551639557</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>92761.00423785939</v>
+        <v>92761.00423785936</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>97891.96859761899</v>
+        <v>97891.96859761898</v>
       </c>
       <c r="AF39" s="165" t="n">
         <v>114751.0920171928</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>133451.6144859162</v>
+        <v>133451.6144859161</v>
       </c>
       <c r="AH39" s="166" t="n">
         <v>148896.2470603794</v>
@@ -4918,46 +4918,46 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>229.300384964129</v>
+        <v>229.3003849641289</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>347.2212936759051</v>
+        <v>347.221293675905</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>379.8917737149281</v>
+        <v>379.8917737149279</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>410.1189307766605</v>
+        <v>410.1189307766604</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>441.6747640809032</v>
+        <v>441.674764080903</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>229.300384964129</v>
+        <v>229.3003849641289</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>347.2212936759051</v>
+        <v>347.221293675905</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>379.8917737149281</v>
+        <v>379.8917737149279</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>410.1189307766605</v>
+        <v>410.1189307766604</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>441.6747640809032</v>
+        <v>441.674764080903</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>687.6601186702486</v>
+        <v>687.6601186702484</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687163</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>869.2810738962293</v>
+        <v>869.2810738962287</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063706</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>1052.062863383992</v>
@@ -4968,46 +4968,46 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>38.21673082735484</v>
+        <v>38.21673082735482</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>57.87021561265087</v>
+        <v>57.87021561265084</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>63.3152956191547</v>
+        <v>63.31529561915465</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>68.35315512944344</v>
+        <v>68.35315512944339</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>73.61246068015053</v>
+        <v>73.61246068015051</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>38.21673082735484</v>
+        <v>38.21673082735482</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>57.87021561265087</v>
+        <v>57.87021561265084</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>63.3152956191547</v>
+        <v>63.31529561915465</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>68.35315512944344</v>
+        <v>68.35315512944339</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>73.61246068015053</v>
+        <v>73.61246068015051</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>687.6601186702486</v>
+        <v>687.6601186702484</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687163</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>869.2810738962293</v>
+        <v>869.2810738962287</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063706</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>1052.062863383992</v>
@@ -5023,22 +5023,22 @@
         <v>297.9288864996687</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>328.0617592449053</v>
+        <v>328.0617592449051</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>381.8221680697479</v>
+        <v>381.8221680697478</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>448.8688390305693</v>
+        <v>448.8688390305692</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>500.4902004560173</v>
+        <v>500.4902004560172</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>250.9487587914139</v>
+        <v>250.9487587914138</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>228.3335186840541</v>
+        <v>228.333518684054</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>226.3945671991866</v>
@@ -5050,10 +5050,10 @@
         <v>261.7690304409803</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>93448.66435652964</v>
+        <v>93448.66435652961</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>98663.05884628771</v>
+        <v>98663.05884628769</v>
       </c>
       <c r="O41" s="183" t="n">
         <v>115620.373091089</v>
@@ -5070,40 +5070,40 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>308.6423315765015</v>
+        <v>308.6423315765014</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>344.5994690405944</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>400.9222464547476</v>
+        <v>400.9222464547475</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>470.1612161285221</v>
+        <v>470.161216128522</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>524.4045823348487</v>
+        <v>524.4045823348486</v>
       </c>
       <c r="Y41" s="185" t="n">
         <v>258.5069579600629</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>236.2239125205443</v>
+        <v>236.2239125205442</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>232.9755413584234</v>
+        <v>232.9755413584233</v>
       </c>
       <c r="AB41" s="186" t="n">
         <v>253.9190277323865</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>268.1651670840907</v>
+        <v>268.1651670840906</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>93448.66435652964</v>
+        <v>93448.66435652961</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>98663.05884628771</v>
+        <v>98663.05884628769</v>
       </c>
       <c r="AF41" s="189" t="n">
         <v>115620.373091089</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.06214434575962195</v>
+        <v>0.06214434575962192</v>
       </c>
       <c r="D57" s="149" t="n">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.05641921194822883</v>
+        <v>0.05641921194822881</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>9.473945063523477</v>
+        <v>9.473945063523473</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.06668742670381966</v>
+        <v>0.06668742670381964</v>
       </c>
       <c r="U57" s="149" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.06013872536685885</v>
+        <v>0.06013872536685883</v>
       </c>
       <c r="Z57" s="149" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>9.473945063523477</v>
+        <v>9.473945063523473</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>0.6708443804947056</v>
+        <v>0.6708443804947054</v>
       </c>
       <c r="D58" s="156" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.5047408395681511</v>
+        <v>0.504740839568151</v>
       </c>
       <c r="I58" s="156" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>54.81635367607643</v>
+        <v>54.81635367607642</v>
       </c>
       <c r="N58" s="159" t="n">
         <v>0</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>0.6756768072129592</v>
+        <v>0.675676807212959</v>
       </c>
       <c r="U58" s="156" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.5074716067372811</v>
+        <v>0.507471606737281</v>
       </c>
       <c r="Z58" s="156" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>54.81635367607643</v>
+        <v>54.81635367607642</v>
       </c>
       <c r="AE58" s="159" t="n">
         <v>0</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>64.2902987395999</v>
+        <v>64.29029873959989</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.2880480008943458</v>
+        <v>0.2880480008943457</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.2420993129083912</v>
+        <v>0.2420993129083911</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>64.2902987395999</v>
+        <v>64.29029873959989</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.1740480325067189</v>
+        <v>0.1740480325067188</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0</v>
@@ -6772,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>64.2902987395999</v>
+        <v>64.29029873959989</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.2257545552511648</v>
+        <v>0.2257545552511647</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.1871623796096995</v>
+        <v>0.1871623796096994</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>64.2902987395999</v>
+        <v>64.29029873959989</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>0</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.1726463484751185</v>
+        <v>0.1726463484751184</v>
       </c>
       <c r="I63" s="180" t="n">
         <v>0</v>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>64.2902987395999</v>
+        <v>64.29029873959989</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>0</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.2123380557375879</v>
+        <v>0.2123380557375878</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>64.2902987395999</v>
+        <v>64.29029873959989</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>0</v>
@@ -7297,10 +7297,10 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.8434271547878566</v>
+        <v>0.8434271547878563</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.5076327417923732</v>
+        <v>0.5076327417923728</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>0.2386522012331493</v>
@@ -7309,28 +7309,28 @@
         <v>0.1110105443255847</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.1289246844412498</v>
+        <v>0.1289246844412497</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.7657252615214782</v>
+        <v>0.7657252615214781</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.3659324586341772</v>
+        <v>0.3659324586341769</v>
       </c>
       <c r="J68" s="149" t="n">
         <v>0.1393239773741763</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.05941474593456195</v>
+        <v>0.05941474593456193</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.06360697153776257</v>
+        <v>0.06360697153776254</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>128.5810065561253</v>
+        <v>128.5810065561252</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>70.62983584535287</v>
+        <v>70.62983584535283</v>
       </c>
       <c r="O68" s="152" t="n">
         <v>32.4179268437376</v>
@@ -7339,7 +7339,7 @@
         <v>14.49709395855619</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>15.94387757167488</v>
+        <v>15.94387757167487</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.9050861486657079</v>
+        <v>0.9050861486657077</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.5447433848878583</v>
+        <v>0.544743384887858</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>0.2560989416318168</v>
@@ -7359,28 +7359,28 @@
         <v>0.1191260033004262</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.1383497619758549</v>
+        <v>0.1383497619758548</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.8162067426847849</v>
+        <v>0.8162067426847847</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.3848309810879126</v>
+        <v>0.3848309810879124</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.145094537871772</v>
+        <v>0.1450945378717719</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.06166308483679255</v>
+        <v>0.06166308483679254</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.06581918830017978</v>
+        <v>0.06581918830017976</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>128.5810065561253</v>
+        <v>128.5810065561252</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>70.62983584535287</v>
+        <v>70.62983584535283</v>
       </c>
       <c r="AF68" s="152" t="n">
         <v>32.4179268437376</v>
@@ -7389,7 +7389,7 @@
         <v>14.49709395855619</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>15.94387757167488</v>
+        <v>15.94387757167487</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>1.527013027016195</v>
+        <v>1.527013027016194</v>
       </c>
       <c r="D69" s="156" t="n">
         <v>0.8375728786571767</v>
@@ -7408,10 +7408,10 @@
         <v>0.9144990536095222</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>0.9634757857672663</v>
+        <v>0.963475785767266</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>1.019626663649774</v>
+        <v>1.019626663649775</v>
       </c>
       <c r="H69" s="155" t="n">
         <v>1.14891897390462</v>
@@ -7423,13 +7423,13 @@
         <v>0.5038337079856268</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>0.5185172297128532</v>
+        <v>0.518517229712853</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>0.5402681549517182</v>
+        <v>0.5402681549517186</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>124.7760115321655</v>
+        <v>124.7760115321654</v>
       </c>
       <c r="N69" s="159" t="n">
         <v>66.95943787995972</v>
@@ -7438,10 +7438,10 @@
         <v>75.4349224130135</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>82.71716419582474</v>
+        <v>82.71716419582471</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>90.58922323081399</v>
+        <v>90.58922323081407</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>1.538012863588475</v>
+        <v>1.538012863588474</v>
       </c>
       <c r="U69" s="156" t="n">
         <v>0.8436063339189213</v>
@@ -7458,10 +7458,10 @@
         <v>0.9210866464834782</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>0.97041618247462</v>
+        <v>0.9704161824746197</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>1.026971543140948</v>
+        <v>1.026971543140949</v>
       </c>
       <c r="Y69" s="155" t="n">
         <v>1.155134896944677</v>
@@ -7473,13 +7473,13 @@
         <v>0.5058268217051225</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>0.5205207173749056</v>
+        <v>0.5205207173749054</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>0.5423233486195682</v>
+        <v>0.5423233486195687</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>124.7760115321655</v>
+        <v>124.7760115321654</v>
       </c>
       <c r="AE69" s="159" t="n">
         <v>66.95943787995972</v>
@@ -7488,10 +7488,10 @@
         <v>75.4349224130135</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>82.71716419582474</v>
+        <v>82.71716419582471</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>90.58922323081399</v>
+        <v>90.58922323081407</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,34 +7501,34 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>1.081968112357209</v>
+        <v>1.081968112357208</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.6280312203044942</v>
+        <v>0.628031220304494</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.4940008408570776</v>
+        <v>0.4940008408570775</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.4491408680646117</v>
+        <v>0.4491408680646116</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.501300071893986</v>
+        <v>0.5013000718939863</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.9162223153774056</v>
+        <v>0.9162223153774054</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.4270931923761338</v>
+        <v>0.4270931923761337</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.28204046834055</v>
+        <v>0.2820404683405499</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.2409128390188602</v>
+        <v>0.2409128390188601</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.2546585795124507</v>
+        <v>0.2546585795124509</v>
       </c>
       <c r="M70" s="164" t="n">
         <v>253.3570180882907</v>
@@ -7540,7 +7540,7 @@
         <v>107.8528492567511</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>97.21425815438093</v>
+        <v>97.2142581543809</v>
       </c>
       <c r="Q70" s="166" t="n">
         <v>106.5331008024889</v>
@@ -7554,19 +7554,19 @@
         <v>1.135147666189533</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.6582276306218704</v>
+        <v>0.6582276306218703</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.5173261222854663</v>
+        <v>0.5173261222854662</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.4697831649815755</v>
+        <v>0.4697831649815754</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.5236242886542315</v>
+        <v>0.5236242886542319</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.9540717838026294</v>
+        <v>0.9540717838026291</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>0.4408465282653755</v>
@@ -7575,10 +7575,10 @@
         <v>0.2894926558403267</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.2467279264872337</v>
+        <v>0.2467279264872336</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.2602960538354858</v>
+        <v>0.260296053835486</v>
       </c>
       <c r="AD70" s="164" t="n">
         <v>253.3570180882907</v>
@@ -7590,7 +7590,7 @@
         <v>107.8528492567511</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>97.21425815438093</v>
+        <v>97.2142581543809</v>
       </c>
       <c r="AH70" s="166" t="n">
         <v>106.5331008024889</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.6733796218804904</v>
+        <v>0.6733796218804905</v>
       </c>
       <c r="D71" s="156" t="n">
         <v>0.9571440170984303</v>
@@ -7612,25 +7612,25 @@
         <v>1.356887111150443</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>2.390163817245792</v>
+        <v>2.390163817245793</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>4.103085148771918</v>
+        <v>4.103085148771919</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.5547423026400455</v>
+        <v>0.5547423026400454</v>
       </c>
       <c r="I71" s="156" t="n">
         <v>0.7058546822306387</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.8851035230875922</v>
+        <v>0.885103523087592</v>
       </c>
       <c r="K71" s="156" t="n">
         <v>1.406820280928509</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>2.284965693405784</v>
+        <v>2.284965693405785</v>
       </c>
       <c r="M71" s="158" t="n">
         <v>51.51280976610926</v>
@@ -7645,7 +7645,7 @@
         <v>192.7906562953858</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>347.5611327190495</v>
+        <v>347.5611327190496</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7662,13 +7662,13 @@
         <v>1.685437207274348</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>2.968906547908311</v>
+        <v>2.968906547908312</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>5.096586383292903</v>
+        <v>5.096586383292905</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.660872222162846</v>
+        <v>0.6608722221628462</v>
       </c>
       <c r="Z71" s="156" t="n">
         <v>0.8243619451887233</v>
@@ -7680,7 +7680,7 @@
         <v>1.58915351122583</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>2.563221555416163</v>
+        <v>2.563221555416164</v>
       </c>
       <c r="AD71" s="158" t="n">
         <v>51.51280976610926</v>
@@ -7695,7 +7695,7 @@
         <v>192.7906562953858</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>347.5611327190495</v>
+        <v>347.5611327190496</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,13 +7705,13 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.9813553133224946</v>
+        <v>0.9813553133224944</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.7156157657092143</v>
+        <v>0.715615765709214</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.7300156140825068</v>
+        <v>0.7300156140825067</v>
       </c>
       <c r="F72" s="162" t="n">
         <v>0.9761026487501234</v>
@@ -7720,10 +7720,10 @@
         <v>1.527800461722212</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.8253499322447014</v>
+        <v>0.8253499322447011</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.4969502876793459</v>
+        <v>0.4969502876793458</v>
       </c>
       <c r="J72" s="162" t="n">
         <v>0.4315121284869898</v>
@@ -7732,10 +7732,10 @@
         <v>0.5364852044943706</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.7960353754855557</v>
+        <v>0.7960353754855558</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>304.8698278544</v>
+        <v>304.8698278543999</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>213.6289355165229</v>
@@ -7747,7 +7747,7 @@
         <v>290.0049144497667</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>454.0942335215384</v>
+        <v>454.0942335215386</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7758,10 +7758,10 @@
         <v>1.070546470402006</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.7825585376733135</v>
+        <v>0.7825585376733134</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.7987687043849911</v>
+        <v>0.798768704384991</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>1.066700818068707</v>
@@ -7770,22 +7770,22 @@
         <v>1.671626092331173</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.8875392333071004</v>
+        <v>0.8875392333071001</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.5283358554219204</v>
+        <v>0.5283358554219203</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.4546435921901263</v>
+        <v>0.4546435921901262</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.5627551092749424</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.8333960145021296</v>
+        <v>0.83339601450213</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>304.8698278544</v>
+        <v>304.8698278543999</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>213.6289355165229</v>
@@ -7797,7 +7797,7 @@
         <v>290.0049144497667</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>454.0942335215384</v>
+        <v>454.0942335215386</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>22.52427460963667</v>
+        <v>22.52427460963666</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>32.52028395838352</v>
+        <v>32.52028395838351</v>
       </c>
       <c r="E73" s="156" t="n">
         <v>33.86831783406382</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>35.35776816236777</v>
+        <v>35.35776816236775</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>36.92500467223028</v>
+        <v>36.92500467223027</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>22.52427460963667</v>
+        <v>22.52427460963666</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>32.52028395838352</v>
+        <v>32.52028395838351</v>
       </c>
       <c r="J73" s="156" t="n">
         <v>33.86831783406382</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>35.35776816236777</v>
+        <v>35.35776816236775</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>36.92500467223028</v>
+        <v>36.92500467223027</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>67.54914673800951</v>
+        <v>67.54914673800948</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121332</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>82.54761814889748</v>
+        <v>82.54761814889746</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>87.95482401348623</v>
+        <v>87.9548240134862</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>3.754045768272778</v>
+        <v>3.754045768272777</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>5.420047326397254</v>
+        <v>5.420047326397252</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>5.644719639010638</v>
+        <v>5.644719639010637</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>5.892961360394628</v>
+        <v>5.892961360394627</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>6.154167445371714</v>
+        <v>6.154167445371712</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>3.754045768272778</v>
+        <v>3.754045768272777</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>5.420047326397254</v>
+        <v>5.420047326397252</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>5.644719639010638</v>
+        <v>5.644719639010637</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>5.892961360394628</v>
+        <v>5.892961360394627</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>6.154167445371714</v>
+        <v>6.154167445371712</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>67.54914673800951</v>
+        <v>67.54914673800948</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121332</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>82.54761814889748</v>
+        <v>82.54761814889746</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>87.95482401348623</v>
+        <v>87.9548240134862</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7912,22 +7912,22 @@
         <v>1.187329655010871</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.9504658730338159</v>
+        <v>0.9504658730338155</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.9804288971651034</v>
+        <v>0.9804288971651033</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>1.244165984092921</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>1.809225069629853</v>
+        <v>1.809225069629854</v>
       </c>
       <c r="H74" s="179" t="n">
         <v>1.00010075122926</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.6615315899007601</v>
+        <v>0.66153158990076</v>
       </c>
       <c r="J74" s="180" t="n">
         <v>0.5813276294704895</v>
@@ -7936,22 +7936,22 @@
         <v>0.6862277568899725</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.946270460230802</v>
+        <v>0.9462704602308021</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>372.4189745924095</v>
+        <v>372.4189745924094</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>285.8482213177363</v>
+        <v>285.8482213177362</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>296.8857346669486</v>
+        <v>296.8857346669485</v>
       </c>
       <c r="P74" s="183" t="n">
         <v>372.5525325986642</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>542.0490575350246</v>
+        <v>542.0490575350248</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>1.230025719821854</v>
+        <v>1.230025719821853</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.9983791952543596</v>
+        <v>0.9983791952543594</v>
       </c>
       <c r="V74" s="186" t="n">
         <v>1.029473374811439</v>
@@ -7977,31 +7977,31 @@
         <v>1.030222281628178</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.6843917674589183</v>
+        <v>0.6843917674589182</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.598226012479079</v>
+        <v>0.5982260124790788</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.7038078599995387</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.9693918934835403</v>
+        <v>0.9693918934835405</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>372.4189745924095</v>
+        <v>372.4189745924094</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>285.8482213177363</v>
+        <v>285.8482213177362</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>296.8857346669486</v>
+        <v>296.8857346669485</v>
       </c>
       <c r="AG74" s="189" t="n">
         <v>372.5525325986642</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>542.0490575350246</v>
+        <v>542.0490575350248</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,28 +8260,28 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>172.784862292404</v>
+        <v>172.7848622924039</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>179.7296438221846</v>
+        <v>179.7296438221845</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>196.1465345738421</v>
+        <v>196.146534573842</v>
       </c>
       <c r="F79" s="149" t="n">
         <v>199.4256401526904</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>213.3215874713197</v>
+        <v>213.3215874713196</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>156.8668178570583</v>
+        <v>156.8668178570582</v>
       </c>
       <c r="I79" s="149" t="n">
         <v>129.5600244796603</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>114.5093789363011</v>
+        <v>114.509378936301</v>
       </c>
       <c r="K79" s="149" t="n">
         <v>106.7360205689818</v>
@@ -8290,19 +8290,19 @@
         <v>105.2454787962793</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>26341.16222734956</v>
+        <v>26341.16222734954</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>25006.80944039012</v>
+        <v>25006.80944039011</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>26644.06184234361</v>
+        <v>26644.06184234359</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>26043.40209844784</v>
+        <v>26043.40209844783</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>26381.08666915488</v>
+        <v>26381.08666915487</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,28 +8310,28 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>185.4163512192128</v>
+        <v>185.4163512192127</v>
       </c>
       <c r="U79" s="149" t="n">
         <v>192.8688330754495</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>210.4858855252497</v>
+        <v>210.4858855252496</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>214.0047110961131</v>
+        <v>214.004711096113</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>228.9165257908192</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>167.2084765546757</v>
+        <v>167.2084765546756</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>136.2511309228391</v>
+        <v>136.251130922839</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>119.2521612710272</v>
+        <v>119.2521612710271</v>
       </c>
       <c r="AB79" s="149" t="n">
         <v>110.7750641353523</v>
@@ -8340,19 +8340,19 @@
         <v>108.9058607753762</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>26341.16222734956</v>
+        <v>26341.16222734954</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>25006.80944039012</v>
+        <v>25006.80944039011</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>26644.06184234361</v>
+        <v>26644.06184234359</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>26043.40209844784</v>
+        <v>26043.40209844783</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>26381.08666915488</v>
+        <v>26381.08666915487</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8371,10 +8371,10 @@
         <v>311.4000205947125</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>347.3623777653925</v>
+        <v>347.3623777653924</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>373.3680918579745</v>
+        <v>373.3680918579744</v>
       </c>
       <c r="H80" s="155" t="n">
         <v>206.5575802734972</v>
@@ -8386,10 +8386,10 @@
         <v>171.5625909330092</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>186.9412604717898</v>
+        <v>186.9412604717897</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>197.8360289087525</v>
+        <v>197.8360289087524</v>
       </c>
       <c r="M80" s="158" t="n">
         <v>22432.76645581946</v>
@@ -8401,10 +8401,10 @@
         <v>25686.67107992767</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>29822.05807506683</v>
+        <v>29822.05807506682</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>33172.06839169405</v>
+        <v>33172.06839169403</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>349.8646022514822</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>376.0576484754233</v>
+        <v>376.0576484754232</v>
       </c>
       <c r="Y80" s="155" t="n">
         <v>207.6751055746565</v>
@@ -8439,7 +8439,7 @@
         <v>187.6635788199981</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>198.588602145134</v>
+        <v>198.5886021451339</v>
       </c>
       <c r="AD80" s="158" t="n">
         <v>22432.76645581946</v>
@@ -8451,10 +8451,10 @@
         <v>25686.67107992767</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>29822.05807506683</v>
+        <v>29822.05807506682</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>33172.06839169405</v>
+        <v>33172.06839169403</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>208.2904035884389</v>
+        <v>208.2904035884388</v>
       </c>
       <c r="D81" s="162" t="n">
         <v>215.133135766275</v>
@@ -8473,10 +8473,10 @@
         <v>239.6916376750332</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>258.1047446488243</v>
+        <v>258.1047446488242</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>280.232159663373</v>
+        <v>280.2321596633728</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>176.3825695666051</v>
@@ -8491,22 +8491,22 @@
         <v>138.4437516575337</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>142.3568990204986</v>
+        <v>142.3568990204985</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>48773.92868316901</v>
+        <v>48773.928683169</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>47131.43383219007</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>52330.73292227127</v>
+        <v>52330.73292227126</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>55865.46017351467</v>
+        <v>55865.46017351466</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>59553.15506084893</v>
+        <v>59553.15506084891</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>218.5280349972388</v>
+        <v>218.5280349972387</v>
       </c>
       <c r="U81" s="162" t="n">
         <v>225.4769661849485</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>251.0091789470309</v>
+        <v>251.0091789470308</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>269.9671137930005</v>
+        <v>269.9671137930004</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>292.7116381758753</v>
+        <v>292.7116381758751</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>183.6689959999333</v>
+        <v>183.6689959999332</v>
       </c>
       <c r="Z81" s="162" t="n">
         <v>151.012709163445</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>140.4632604529069</v>
+        <v>140.4632604529068</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>141.7854686395635</v>
+        <v>141.7854686395634</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>145.5083081129055</v>
+        <v>145.5083081129054</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>48773.92868316901</v>
+        <v>48773.928683169</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>47131.43383219007</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>52330.73292227127</v>
+        <v>52330.73292227126</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>55865.46017351467</v>
+        <v>55865.46017351466</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>59553.15506084893</v>
+        <v>59553.15506084891</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,13 +8566,13 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>579.82830575</v>
+        <v>579.8283057500001</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>641.6337824716056</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>762.0533737760867</v>
+        <v>762.0533737760868</v>
       </c>
       <c r="F82" s="156" t="n">
         <v>965.4865105334821</v>
@@ -8587,7 +8587,7 @@
         <v>473.1787500567564</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>497.0908193962615</v>
+        <v>497.0908193962616</v>
       </c>
       <c r="K82" s="156" t="n">
         <v>568.2731845328248</v>
@@ -8616,13 +8616,13 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>720.2251331824639</v>
+        <v>720.2251331824641</v>
       </c>
       <c r="U82" s="156" t="n">
         <v>796.9958897353818</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>946.5732996772175</v>
+        <v>946.5732996772177</v>
       </c>
       <c r="W82" s="156" t="n">
         <v>1199.264754305847</v>
@@ -8631,13 +8631,13 @@
         <v>1316.773003451275</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>569.0585346551051</v>
+        <v>569.0585346551053</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>552.6216155229816</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>569.5075396539746</v>
+        <v>569.5075396539747</v>
       </c>
       <c r="AB82" s="156" t="n">
         <v>641.9251547466953</v>
@@ -8671,19 +8671,19 @@
         <v>299.7796871958791</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>328.6348458802519</v>
+        <v>328.6348458802518</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>382.5668819938667</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>450.149436924251</v>
+        <v>450.1494369242509</v>
       </c>
       <c r="G83" s="163" t="n">
         <v>502.4893591307167</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>252.1239159319129</v>
+        <v>252.1239159319128</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>228.2162985045395</v>
@@ -8698,10 +8698,10 @@
         <v>261.8138400234657</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>93130.16436445338</v>
+        <v>93130.16436445336</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>98105.59753313551</v>
+        <v>98105.5975331355</v>
       </c>
       <c r="O83" s="165" t="n">
         <v>114970.4791332138</v>
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>327.0253716151248</v>
+        <v>327.0253716151247</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>359.3772199326397</v>
@@ -8727,31 +8727,31 @@
         <v>418.5971461102332</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>491.9306112273324</v>
+        <v>491.9306112273323</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>549.7932124557776</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>271.121203628148</v>
+        <v>271.1212036281479</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>242.6296075904888</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>238.2573442641596</v>
+        <v>238.2573442641595</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>259.5258765978517</v>
+        <v>259.5258765978516</v>
       </c>
       <c r="AC83" s="163" t="n">
         <v>274.1016511784579</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>93130.16436445338</v>
+        <v>93130.16436445336</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>98105.59753313551</v>
+        <v>98105.5975331355</v>
       </c>
       <c r="AF83" s="165" t="n">
         <v>114970.4791332138</v>
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>251.8246595737656</v>
+        <v>251.8246595737655</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>379.7415776342887</v>
+        <v>379.7415776342885</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>413.760091548992</v>
+        <v>413.7600915489917</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>445.4766989390283</v>
+        <v>445.4766989390281</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>478.5997687531334</v>
+        <v>478.5997687531333</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>251.8246595737656</v>
+        <v>251.8246595737655</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>379.7415776342887</v>
+        <v>379.7415776342885</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>413.760091548992</v>
+        <v>413.7600915489917</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>445.4766989390283</v>
+        <v>445.4766989390282</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>478.5997687531334</v>
+        <v>478.5997687531332</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>755.2092654082581</v>
+        <v>755.2092654082578</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699296</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>946.7796925421452</v>
+        <v>946.7796925421446</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>1140.017687397479</v>
+        <v>1140.017687397478</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>41.97077659562761</v>
+        <v>41.9707765956276</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>63.29026293904812</v>
+        <v>63.29026293904809</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>68.96001525816533</v>
+        <v>68.9600152581653</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>74.24611648983806</v>
+        <v>74.24611648983803</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>79.76662812552225</v>
+        <v>79.7666281255222</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>41.97077659562761</v>
+        <v>41.9707765956276</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>63.29026293904812</v>
+        <v>63.29026293904809</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>68.96001525816533</v>
+        <v>68.9600152581653</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>74.24611648983806</v>
+        <v>74.24611648983803</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>79.76662812552225</v>
+        <v>79.7666281255222</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>755.2092654082581</v>
+        <v>755.2092654082578</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699296</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>946.7796925421452</v>
+        <v>946.7796925421446</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>1140.017687397479</v>
+        <v>1140.017687397478</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8875,10 +8875,10 @@
         <v>299.321183633328</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>329.0122251179391</v>
+        <v>329.012225117939</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>382.802596966913</v>
+        <v>382.8025969669129</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>450.1130050146622</v>
@@ -8896,16 +8896,16 @@
         <v>226.9758948286571</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>248.2627251728077</v>
+        <v>248.2627251728076</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>262.7153009012112</v>
+        <v>262.7153009012111</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>93885.37362986163</v>
+        <v>93885.37362986161</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>98948.90706760544</v>
+        <v>98948.90706760543</v>
       </c>
       <c r="O85" s="183" t="n">
         <v>115917.258825756</v>
@@ -8925,13 +8925,13 @@
         <v>310.0846953520609</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>345.5978482358488</v>
+        <v>345.5978482358487</v>
       </c>
       <c r="V85" s="186" t="n">
         <v>401.951719829559</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>471.464399912476</v>
+        <v>471.4643999124759</v>
       </c>
       <c r="X85" s="187" t="n">
         <v>526.3002556489805</v>
@@ -8940,22 +8940,22 @@
         <v>259.7150264385089</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>236.9083042880032</v>
+        <v>236.9083042880031</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>233.5737673709025</v>
+        <v>233.5737673709024</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>254.6228355923861</v>
+        <v>254.622835592386</v>
       </c>
       <c r="AC85" s="187" t="n">
         <v>269.1345589775742</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>93885.37362986163</v>
+        <v>93885.37362986161</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>98948.90706760544</v>
+        <v>98948.90706760543</v>
       </c>
       <c r="AF85" s="189" t="n">
         <v>115917.258825756</v>
@@ -9636,13 +9636,13 @@
         </is>
       </c>
       <c r="C93" s="79" t="n">
-        <v>76.49891397404303</v>
+        <v>76.49891397404302</v>
       </c>
       <c r="D93" s="80" t="n">
         <v>79.4443264888429</v>
       </c>
       <c r="E93" s="80" t="n">
-        <v>82.19863380507508</v>
+        <v>82.19863380507506</v>
       </c>
       <c r="F93" s="80" t="n">
         <v>80.66001790519121</v>
@@ -9686,13 +9686,13 @@
         </is>
       </c>
       <c r="T93" s="79" t="n">
-        <v>61.58662567812256</v>
+        <v>61.58662567812254</v>
       </c>
       <c r="U93" s="80" t="n">
         <v>63.95787526315834</v>
       </c>
       <c r="V93" s="80" t="n">
-        <v>66.17527267281126</v>
+        <v>66.17527267281125</v>
       </c>
       <c r="W93" s="80" t="n">
         <v>64.93658631027404</v>
@@ -9716,7 +9716,7 @@
         <v>67.40054441000001</v>
       </c>
       <c r="AD93" s="79" t="n">
-        <v>77.94670140246257</v>
+        <v>77.94670140246254</v>
       </c>
       <c r="AE93" s="80" t="n">
         <v>92.24062589861833</v>
@@ -9759,7 +9759,7 @@
         <v>310.6620239536148</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>298.5246353604367</v>
+        <v>298.5246353604368</v>
       </c>
       <c r="E94" s="86" t="n">
         <v>300.5238679678944</v>
@@ -9792,13 +9792,13 @@
         <v>429.8798910332167</v>
       </c>
       <c r="O94" s="86" t="n">
-        <v>508.4147154571744</v>
+        <v>508.4147154571743</v>
       </c>
       <c r="P94" s="86" t="n">
         <v>540.5646083438444</v>
       </c>
       <c r="Q94" s="87" t="n">
-        <v>570.444791155865</v>
+        <v>570.4447911558651</v>
       </c>
       <c r="S94" s="42" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>313.660972772553</v>
       </c>
       <c r="D96" s="133" t="n">
-        <v>300.7453812153509</v>
+        <v>300.745381215351</v>
       </c>
       <c r="E96" s="133" t="n">
         <v>302.8121014439594</v>
@@ -10030,7 +10030,7 @@
         <v>542.899247164084</v>
       </c>
       <c r="Q96" s="134" t="n">
-        <v>572.8267766097391</v>
+        <v>572.8267766097392</v>
       </c>
       <c r="S96" s="51" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>417.6675332888115</v>
       </c>
       <c r="AF96" s="136" t="n">
-        <v>496.2768727435288</v>
+        <v>496.2768727435289</v>
       </c>
       <c r="AG96" s="136" t="n">
         <v>529.3384086374205</v>
